--- a/files/港岛-赤柱-Solace.xlsx
+++ b/files/港岛-赤柱-Solace.xlsx
@@ -106,19 +106,18 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00000000"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -242,13 +241,13 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -810,23 +809,19 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>96800000</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>39286</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -835,12 +830,12 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -850,7 +845,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -880,7 +875,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -890,12 +885,12 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -905,12 +900,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -920,7 +915,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1090,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1204,27 +1199,27 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
+          <t>0 套</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
           <t>1 套</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
+          <t>2 套</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
+        <is>
+          <t>2 套</t>
+        </is>
+      </c>
+      <c r="F3" s="11" t="inlineStr">
+        <is>
           <t>1 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>2 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>2 套</t>
         </is>
       </c>
     </row>
@@ -1284,21 +1279,21 @@
         <is>
           <t>52B号屋
 2464呎 (4+房)
-(在售)
-招标项目
--</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
+(26年-07月-29日)
+$9,680万
+$39,286/呎</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
         <is>
           <t>52C号屋
 2362呎 (4+房)
-(待售)
-暂无价格
-暂无呎价</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="inlineStr">
+(已定价未售)
+招标单位
+-</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>52D号屋
 2496呎 (4+房)
@@ -1307,7 +1302,7 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>52E号屋
 2496呎 (4+房)
@@ -1316,11 +1311,11 @@
 暂无呎价</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="G6" s="17" t="inlineStr">
         <is>
           <t>54号屋
 2784呎 (4+房)
-(25年-07月-31日)
+(25年-08月-01日)
 $1.20亿
 $43,103/呎</t>
         </is>

--- a/files/港岛-赤柱-Solace.xlsx
+++ b/files/港岛-赤柱-Solace.xlsx
@@ -111,7 +111,8 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
@@ -244,7 +245,7 @@
     <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -875,7 +876,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1199,12 +1200,12 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
+          <t>1 套</t>
+        </is>
+      </c>
+      <c r="C3" s="13" t="inlineStr">
+        <is>
           <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>1 套</t>
         </is>
       </c>
       <c r="D3" s="14" t="inlineStr">
@@ -1288,8 +1289,8 @@
         <is>
           <t>52C号屋
 2362呎 (4+房)
-(已定价未售)
-招标单位
+(在售)
+招标项目
 -</t>
         </is>
       </c>

--- a/files/港岛-赤柱-Solace.xlsx
+++ b/files/港岛-赤柱-Solace.xlsx
@@ -815,7 +815,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -1280,7 +1280,7 @@
         <is>
           <t>52B号屋
 2464呎 (4+房)
-(26年-07月-29日)
+(26年-08月-14日)
 $9,680万
 $39,286/呎</t>
         </is>
